--- a/docs/workbook-split/dateien/Referenzen.xlsx
+++ b/docs/workbook-split/dateien/Referenzen.xlsx
@@ -9479,6 +9479,8 @@
         <v>1</v>
       </c>
     </row>
+    <row r="399"/>
+    <row r="400"/>
     <row r="401">
       <c r="C401" t="inlineStr">
         <is>
